--- a/data/valuations/PYPL/PYPL_modelo_valoracion.xlsx
+++ b/data/valuations/PYPL/PYPL_modelo_valoracion.xlsx
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.067</v>
+        <v>0.052</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.06030000000000001</v>
+        <v>0.0468</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.05360000000000001</v>
+        <v>0.0416</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.0469</v>
+        <v>0.03639999999999999</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.0402</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.022</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.006299999999999999</v>
+        <v>0.0198</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.0056</v>
+        <v>0.0176</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.004899999999999999</v>
+        <v>0.0154</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.0042</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="11">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.4920039526873513</v>
+        <v>0.4820039526873512</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.4920039526873513</v>
+        <v>0.4820039526873512</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.4920039526873513</v>
+        <v>0.4820039526873512</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.4920039526873513</v>
+        <v>0.4820039526873512</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.4920039526873513</v>
+        <v>0.4820039526873512</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.4520039526873512</v>
+        <v>0.4620039526873512</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.4520039526873512</v>
+        <v>0.4620039526873512</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.4520039526873512</v>
+        <v>0.4620039526873512</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.4520039526873512</v>
+        <v>0.4620039526873512</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.4520039526873512</v>
+        <v>0.4620039526873512</v>
       </c>
     </row>
     <row r="18">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.1267889733229551</v>
+        <v>0.1317889733229551</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.1267889733229551</v>
+        <v>0.1317889733229551</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.1267889733229551</v>
+        <v>0.1317889733229551</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.1267889733229551</v>
+        <v>0.1317889733229551</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.1267889733229551</v>
+        <v>0.1317889733229551</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.1467889733229551</v>
+        <v>0.1417889733229551</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.1467889733229551</v>
+        <v>0.1417889733229551</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.1467889733229551</v>
+        <v>0.1417889733229551</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.1467889733229551</v>
+        <v>0.1417889733229551</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.1467889733229551</v>
+        <v>0.1417889733229551</v>
       </c>
     </row>
     <row r="23">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.1063266614308248</v>
+        <v>0.1013266614308247</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.1063266614308248</v>
+        <v>0.1013266614308247</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.1063266614308248</v>
+        <v>0.1013266614308247</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.1063266614308248</v>
+        <v>0.1013266614308247</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.1063266614308248</v>
+        <v>0.1013266614308247</v>
       </c>
     </row>
     <row r="28">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.0234366662741051</v>
+        <v>0.02356797406766706</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.0234366662741051</v>
+        <v>0.02356797406766706</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.0234366662741051</v>
+        <v>0.02356797406766706</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.0234366662741051</v>
+        <v>0.02356797406766706</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.0234366662741051</v>
+        <v>0.02356797406766706</v>
       </c>
     </row>
     <row r="32">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.106</v>
+        <v>0.1081</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.096</v>
+        <v>0.09810000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.126</v>
+        <v>0.1181</v>
       </c>
     </row>
     <row r="38">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>45.42</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="4">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="K21" s="8">
-        <f>K12*$C$16</f>
+        <f>K8*$C$16</f>
         <v/>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/45.42-1</f>
+        <f>C33/43.59-1</f>
         <v/>
       </c>
     </row>
@@ -3753,176 +3753,176 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.076</v>
+        <v>0.0781</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*6/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*6/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*8/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*8/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*10/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*10/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*12/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*12/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*14/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*14/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0881</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*6/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*6/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*8/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*8/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*10/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*10/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*12/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*12/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*14/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*14/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.096</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*6/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*6/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*8/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*8/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*10/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*10/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*12/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*12/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*14/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*14/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.106</v>
+        <v>0.1081</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*6/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*6/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*8/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*8/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*10/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*10/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*12/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*12/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*14/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*14/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.116</v>
+        <v>0.1181</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*6/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*6/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*8/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*8/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*10/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*10/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*12/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*12/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*14/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*14/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.126</v>
+        <v>0.1281</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*6/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*6/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*8/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*8/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*10/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*10/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*12/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*12/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*14/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*14/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.136</v>
+        <v>0.1381</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*6/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*6/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*8/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*8/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*10/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*10/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*12/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*12/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*14/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*14/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/PYPL/PYPL_modelo_valoracion.xlsx
+++ b/data/valuations/PYPL/PYPL_modelo_valoracion.xlsx
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.1081</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.09570000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.1181</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="38">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>43.59</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="4">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/43.59-1</f>
+        <f>C33/45.34-1</f>
         <v/>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.0781</v>
+        <v>0.0757</v>
       </c>
       <c r="C39" s="22">
         <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*6/(1+$A$39)^5+$C$29)/$C$32</f>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.0881</v>
+        <v>0.0857</v>
       </c>
       <c r="C40" s="22">
         <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*6/(1+$A$40)^5+$C$29)/$C$32</f>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.09570000000000001</v>
       </c>
       <c r="C41" s="22">
         <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*6/(1+$A$41)^5+$C$29)/$C$32</f>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.1081</v>
+        <v>0.1057</v>
       </c>
       <c r="C42" s="22">
         <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*6/(1+$A$42)^5+$C$29)/$C$32</f>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.1181</v>
+        <v>0.1157</v>
       </c>
       <c r="C43" s="22">
         <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*6/(1+$A$43)^5+$C$29)/$C$32</f>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1281</v>
+        <v>0.1257</v>
       </c>
       <c r="C44" s="22">
         <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*6/(1+$A$44)^5+$C$29)/$C$32</f>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1381</v>
+        <v>0.1357</v>
       </c>
       <c r="C45" s="22">
         <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*6/(1+$A$45)^5+$C$29)/$C$32</f>
